--- a/education_forms/034_child_safety_checklist_form--education_forms.xlsx
+++ b/education_forms/034_child_safety_checklist_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -993,8 +993,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'safe_environment',_'value':_'safe'}</t>
+          <t>safe_environment</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Safe Environment', 'value': 'safe'}</t>
+          <t>Safe Environment</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'minor_changes_needed',_'value':_'minor'}</t>
+          <t>minor_changes_needed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Minor changes needed', 'value': 'minor'}</t>
+          <t>Minor changes needed</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'urgent_action_required',_'value':_'urgent'}</t>
+          <t>urgent_action_required</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Urgent action required', 'value': 'urgent'}</t>
+          <t>Urgent action required</t>
         </is>
       </c>
     </row>
